--- a/artfynd/A 30089-2026 artfynd.xlsx
+++ b/artfynd/A 30089-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1308,50 +1308,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135319564</v>
+        <v>135320059</v>
       </c>
       <c r="B8" t="n">
-        <v>57972</v>
+        <v>79992</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Källan, Källan, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572235</v>
+        <v>572175</v>
       </c>
       <c r="R8" t="n">
-        <v>6339330</v>
+        <v>6339412</v>
       </c>
       <c r="S8" t="n">
         <v>7</v>
@@ -1410,7 +1405,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135319924</v>
+        <v>135319564</v>
       </c>
       <c r="B9" t="n">
         <v>57972</v>
@@ -1441,7 +1436,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1450,13 +1445,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572240</v>
+        <v>572235</v>
       </c>
       <c r="R9" t="n">
-        <v>6339369</v>
+        <v>6339330</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1512,42 +1507,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135317670</v>
+        <v>135319924</v>
       </c>
       <c r="B10" t="n">
-        <v>58136</v>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1556,13 +1547,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572050</v>
+        <v>572240</v>
       </c>
       <c r="R10" t="n">
-        <v>6339338</v>
+        <v>6339369</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1592,11 +1583,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Troligen årsungar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,7 +1609,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135320424</v>
+        <v>135317670</v>
       </c>
       <c r="B11" t="n">
         <v>58136</v>
@@ -1653,7 +1639,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1667,13 +1653,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572031</v>
+        <v>572050</v>
       </c>
       <c r="R11" t="n">
-        <v>6339479</v>
+        <v>6339338</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1703,6 +1689,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Troligen årsungar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1729,7 +1720,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135320583</v>
+        <v>135320424</v>
       </c>
       <c r="B12" t="n">
         <v>58136</v>
@@ -1757,7 +1748,11 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
@@ -1769,13 +1764,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572025</v>
+        <v>572031</v>
       </c>
       <c r="R12" t="n">
-        <v>6339384</v>
+        <v>6339479</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1831,39 +1826,35 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135317700</v>
+        <v>135320583</v>
       </c>
       <c r="B13" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
@@ -1875,10 +1866,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572058</v>
+        <v>572025</v>
       </c>
       <c r="R13" t="n">
-        <v>6339323</v>
+        <v>6339384</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1934,6 +1925,209 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135317700</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Källan, Källan, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>572058</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6339323</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135318035</v>
+      </c>
+      <c r="B15" t="n">
+        <v>111257</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Källan, Källan, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>572058</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6339323</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30089-2026 artfynd.xlsx
+++ b/artfynd/A 30089-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320004</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135319373</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135319458</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320246</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1203,6 +1228,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135316763</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1305,6 +1335,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135319294</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1402,6 +1437,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320059</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1504,6 +1544,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135319564</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1606,6 +1651,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135319924</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1717,6 +1767,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135317670</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1823,6 +1878,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320424</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1925,6 +1985,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320583</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2031,6 +2096,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135317700</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2128,8 +2198,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135318035</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30089-2026 artfynd.xlsx
+++ b/artfynd/A 30089-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135320004</v>
       </c>
       <c r="B2" t="n">
-        <v>92385</v>
+        <v>92427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135319373</v>
       </c>
       <c r="B3" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135319458</v>
       </c>
       <c r="B4" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>135320246</v>
       </c>
       <c r="B5" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>135316763</v>
       </c>
       <c r="B6" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>135319294</v>
       </c>
       <c r="B7" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>135320059</v>
       </c>
       <c r="B8" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>135319564</v>
       </c>
       <c r="B9" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>135319924</v>
       </c>
       <c r="B10" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>135317670</v>
       </c>
       <c r="B11" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>135320424</v>
       </c>
       <c r="B12" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>135320583</v>
       </c>
       <c r="B13" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>135317700</v>
       </c>
       <c r="B14" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>135318035</v>
       </c>
       <c r="B15" t="n">
-        <v>111257</v>
+        <v>111315</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 30089-2026 artfynd.xlsx
+++ b/artfynd/A 30089-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135320004</v>
       </c>
       <c r="B2" t="n">
-        <v>92427</v>
+        <v>92454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135319373</v>
       </c>
       <c r="B3" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135319458</v>
       </c>
       <c r="B4" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>135320246</v>
       </c>
       <c r="B5" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>135316763</v>
       </c>
       <c r="B6" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>135319294</v>
       </c>
       <c r="B7" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>135320059</v>
       </c>
       <c r="B8" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>135318035</v>
       </c>
       <c r="B15" t="n">
-        <v>111315</v>
+        <v>111342</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 30089-2026 artfynd.xlsx
+++ b/artfynd/A 30089-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135320004</v>
       </c>
       <c r="B2" t="n">
-        <v>92459</v>
+        <v>92461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135319373</v>
       </c>
       <c r="B3" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135319458</v>
       </c>
       <c r="B4" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>135320246</v>
       </c>
       <c r="B5" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>135318035</v>
       </c>
       <c r="B15" t="n">
-        <v>111347</v>
+        <v>111349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 30089-2026 artfynd.xlsx
+++ b/artfynd/A 30089-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135316763</v>
+        <v>136175409</v>
       </c>
       <c r="B6" t="n">
-        <v>80060</v>
+        <v>92086</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,37 +1140,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Källan, Källan, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572030</v>
+        <v>572244</v>
       </c>
       <c r="R6" t="n">
-        <v>6339272</v>
+        <v>6339375</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,17 +1203,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På mycket nedbruten stubbe</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,13 +1234,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135316763</t>
+          <t>https://artportalen.se/Sighting/136175409</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135319294</v>
+        <v>135316763</v>
       </c>
       <c r="B7" t="n">
         <v>80060</v>
@@ -1271,13 +1275,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572187</v>
+        <v>572030</v>
       </c>
       <c r="R7" t="n">
-        <v>6339280</v>
+        <v>6339272</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1311,7 +1315,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På låga av enbuske</t>
+          <t>På mycket nedbruten stubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,13 +1341,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135319294</t>
+          <t>https://artportalen.se/Sighting/135316763</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135320059</v>
+        <v>135319294</v>
       </c>
       <c r="B8" t="n">
         <v>80060</v>
@@ -1378,13 +1382,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572175</v>
+        <v>572187</v>
       </c>
       <c r="R8" t="n">
-        <v>6339412</v>
+        <v>6339280</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1414,6 +1418,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På låga av enbuske</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,56 +1448,51 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135320059</t>
+          <t>https://artportalen.se/Sighting/135319294</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135319564</v>
+        <v>135320059</v>
       </c>
       <c r="B9" t="n">
-        <v>57977</v>
+        <v>80060</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Källan, Källan, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572235</v>
+        <v>572175</v>
       </c>
       <c r="R9" t="n">
-        <v>6339330</v>
+        <v>6339412</v>
       </c>
       <c r="S9" t="n">
         <v>7</v>
@@ -1546,59 +1550,54 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135319564</t>
+          <t>https://artportalen.se/Sighting/135320059</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135319924</v>
+        <v>136174852</v>
       </c>
       <c r="B10" t="n">
-        <v>57977</v>
+        <v>80063</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Källan, Källan, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572240</v>
+        <v>572139</v>
       </c>
       <c r="R10" t="n">
-        <v>6339369</v>
+        <v>6339266</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1622,12 +1621,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,16 +1652,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135319924</t>
+          <t>https://artportalen.se/Sighting/136174852</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135317670</v>
+        <v>136175602</v>
       </c>
       <c r="B11" t="n">
-        <v>58141</v>
+        <v>80063</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1670,43 +1669,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Källan, Källan, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572050</v>
+        <v>572174</v>
       </c>
       <c r="R11" t="n">
-        <v>6339338</v>
+        <v>6339415</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,17 +1723,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Troligen årsungar</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,48 +1754,44 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135317670</t>
+          <t>https://artportalen.se/Sighting/136175602</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135320424</v>
+        <v>135319564</v>
       </c>
       <c r="B12" t="n">
-        <v>58141</v>
+        <v>57977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1819,13 +1800,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572031</v>
+        <v>572235</v>
       </c>
       <c r="R12" t="n">
-        <v>6339479</v>
+        <v>6339330</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1880,44 +1861,44 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135320424</t>
+          <t>https://artportalen.se/Sighting/135319564</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135320583</v>
+        <v>135319924</v>
       </c>
       <c r="B13" t="n">
-        <v>58141</v>
+        <v>57977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1926,13 +1907,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572025</v>
+        <v>572240</v>
       </c>
       <c r="R13" t="n">
-        <v>6339384</v>
+        <v>6339369</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1987,16 +1968,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135320583</t>
+          <t>https://artportalen.se/Sighting/135319924</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135317700</v>
+        <v>136174563</v>
       </c>
       <c r="B14" t="n">
-        <v>58136</v>
+        <v>57979</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,16 +1985,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103023</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2021,14 +2002,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2037,13 +2014,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572058</v>
+        <v>572142</v>
       </c>
       <c r="R14" t="n">
-        <v>6339323</v>
+        <v>6339265</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2067,12 +2044,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,54 +2075,63 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135317700</t>
+          <t>https://artportalen.se/Sighting/136174563</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135318035</v>
+        <v>135317670</v>
       </c>
       <c r="B15" t="n">
-        <v>111349</v>
+        <v>58141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219677</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Källan, Källan, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572058</v>
+        <v>572050</v>
       </c>
       <c r="R15" t="n">
-        <v>6339323</v>
+        <v>6339338</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2175,6 +2161,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Troligen årsungar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2199,6 +2190,651 @@
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135317670</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135320424</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Källan, Källan, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>572031</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6339479</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320424</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135320583</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Källan, Källan, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>572025</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6339384</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320583</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136174368</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58143</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Källan, Källan, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>572156</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6339330</v>
+      </c>
+      <c r="S18" t="n">
+        <v>30</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136174368</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136174907</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58143</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Källan, Källan, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>572139</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6339266</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136174907</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135317700</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Källan, Källan, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>572058</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6339323</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135317700</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135318035</v>
+      </c>
+      <c r="B21" t="n">
+        <v>111349</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Källan, Källan, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>572058</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6339323</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135318035</t>
         </is>
@@ -2220,6 +2856,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30089-2026 artfynd.xlsx
+++ b/artfynd/A 30089-2026 artfynd.xlsx
@@ -791,32 +791,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135319373</v>
+        <v>136174079</v>
       </c>
       <c r="B3" t="n">
-        <v>92071</v>
+        <v>92477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572187</v>
+        <v>572047</v>
       </c>
       <c r="R3" t="n">
-        <v>6339280</v>
+        <v>6339366</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,13 +896,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135319373</t>
+          <t>https://artportalen.se/Sighting/136174079</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135319458</v>
+        <v>135319373</v>
       </c>
       <c r="B4" t="n">
         <v>92071</v>
@@ -946,13 +946,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572216</v>
+        <v>572187</v>
       </c>
       <c r="R4" t="n">
-        <v>6339332</v>
+        <v>6339280</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,11 +982,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På död talllåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,13 +1007,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135319458</t>
+          <t>https://artportalen.se/Sighting/135319373</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135320246</v>
+        <v>135319458</v>
       </c>
       <c r="B5" t="n">
         <v>92071</v>
@@ -1048,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1062,13 +1057,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572076</v>
+        <v>572216</v>
       </c>
       <c r="R5" t="n">
-        <v>6339457</v>
+        <v>6339332</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,6 +1093,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På död talllåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,16 +1123,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135320246</t>
+          <t>https://artportalen.se/Sighting/135319458</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136175409</v>
+        <v>135320246</v>
       </c>
       <c r="B6" t="n">
-        <v>92086</v>
+        <v>92071</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572244</v>
+        <v>572076</v>
       </c>
       <c r="R6" t="n">
-        <v>6339375</v>
+        <v>6339457</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,16 +1234,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136175409</t>
+          <t>https://artportalen.se/Sighting/135320246</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135316763</v>
+        <v>136175409</v>
       </c>
       <c r="B7" t="n">
-        <v>80060</v>
+        <v>92087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,37 +1251,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Källan, Källan, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572030</v>
+        <v>572244</v>
       </c>
       <c r="R7" t="n">
-        <v>6339272</v>
+        <v>6339375</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,17 +1314,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På mycket nedbruten stubbe</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,13 +1345,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135316763</t>
+          <t>https://artportalen.se/Sighting/136175409</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135319294</v>
+        <v>135316763</v>
       </c>
       <c r="B8" t="n">
         <v>80060</v>
@@ -1382,13 +1386,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572187</v>
+        <v>572030</v>
       </c>
       <c r="R8" t="n">
-        <v>6339280</v>
+        <v>6339272</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1426,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På låga av enbuske</t>
+          <t>På mycket nedbruten stubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,13 +1452,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135319294</t>
+          <t>https://artportalen.se/Sighting/135316763</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135320059</v>
+        <v>135319294</v>
       </c>
       <c r="B9" t="n">
         <v>80060</v>
@@ -1489,13 +1493,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572175</v>
+        <v>572187</v>
       </c>
       <c r="R9" t="n">
-        <v>6339412</v>
+        <v>6339280</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1525,6 +1529,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På låga av enbuske</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,16 +1559,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135320059</t>
+          <t>https://artportalen.se/Sighting/135319294</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136174852</v>
+        <v>135320059</v>
       </c>
       <c r="B10" t="n">
-        <v>80063</v>
+        <v>80060</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572139</v>
+        <v>572175</v>
       </c>
       <c r="R10" t="n">
-        <v>6339266</v>
+        <v>6339412</v>
       </c>
       <c r="S10" t="n">
         <v>7</v>
@@ -1621,12 +1630,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,13 +1661,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136174852</t>
+          <t>https://artportalen.se/Sighting/135320059</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136175602</v>
+        <v>136174852</v>
       </c>
       <c r="B11" t="n">
         <v>80063</v>
@@ -1693,13 +1702,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572174</v>
+        <v>572139</v>
       </c>
       <c r="R11" t="n">
-        <v>6339415</v>
+        <v>6339266</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1754,7 +1763,7 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136175602</t>
+          <t>https://artportalen.se/Sighting/136174852</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 30089-2026 artfynd.xlsx
+++ b/artfynd/A 30089-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136174079</v>
       </c>
       <c r="B3" t="n">
-        <v>92477</v>
+        <v>92478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136175409</v>
       </c>
       <c r="B7" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>136174852</v>
       </c>
       <c r="B11" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>136174563</v>
       </c>
       <c r="B14" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>136174368</v>
       </c>
       <c r="B18" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>136174907</v>
       </c>
       <c r="B19" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30089-2026 artfynd.xlsx
+++ b/artfynd/A 30089-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136174079</v>
       </c>
       <c r="B3" t="n">
-        <v>92478</v>
+        <v>92484</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136175409</v>
       </c>
       <c r="B7" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>136174852</v>
       </c>
       <c r="B11" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>136174563</v>
       </c>
       <c r="B14" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>136174368</v>
       </c>
       <c r="B18" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>136174907</v>
       </c>
       <c r="B19" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30089-2026 artfynd.xlsx
+++ b/artfynd/A 30089-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136174079</v>
       </c>
       <c r="B3" t="n">
-        <v>92484</v>
+        <v>92485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136175409</v>
       </c>
       <c r="B7" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>136174852</v>
       </c>
       <c r="B11" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>136174563</v>
       </c>
       <c r="B14" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>136174368</v>
       </c>
       <c r="B18" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>136174907</v>
       </c>
       <c r="B19" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30089-2026 artfynd.xlsx
+++ b/artfynd/A 30089-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136174079</v>
       </c>
       <c r="B3" t="n">
-        <v>92485</v>
+        <v>92491</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136175409</v>
       </c>
       <c r="B7" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>136174852</v>
       </c>
       <c r="B11" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 30089-2026 artfynd.xlsx
+++ b/artfynd/A 30089-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136174079</v>
       </c>
       <c r="B3" t="n">
-        <v>92491</v>
+        <v>92498</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136175409</v>
       </c>
       <c r="B7" t="n">
-        <v>92101</v>
+        <v>92108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>136174852</v>
       </c>
       <c r="B11" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>136174563</v>
       </c>
       <c r="B14" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>136174368</v>
       </c>
       <c r="B18" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>136174907</v>
       </c>
       <c r="B19" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30089-2026 artfynd.xlsx
+++ b/artfynd/A 30089-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136174079</v>
       </c>
       <c r="B3" t="n">
-        <v>92498</v>
+        <v>92499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136175409</v>
       </c>
       <c r="B7" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30089-2026 artfynd.xlsx
+++ b/artfynd/A 30089-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136174079</v>
       </c>
       <c r="B3" t="n">
-        <v>92499</v>
+        <v>92512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136175409</v>
       </c>
       <c r="B7" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>136174852</v>
       </c>
       <c r="B11" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>136174563</v>
       </c>
       <c r="B14" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>136174368</v>
       </c>
       <c r="B18" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>136174907</v>
       </c>
       <c r="B19" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30089-2026 artfynd.xlsx
+++ b/artfynd/A 30089-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136174079</v>
       </c>
       <c r="B3" t="n">
-        <v>92512</v>
+        <v>92513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136175409</v>
       </c>
       <c r="B7" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>136174852</v>
       </c>
       <c r="B11" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
